--- a/Altium/DTCP v2.0/Project Outputs for DTCP v2.0/Assembly/BOM/Bill of Materials-DTCP v2.0.xlsx
+++ b/Altium/DTCP v2.0/Project Outputs for DTCP v2.0/Assembly/BOM/Bill of Materials-DTCP v2.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\AppData\Local\TempReleases\Snapshot\3\Assembly\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\AppData\Local\TempReleases\Snapshot\4\Assembly\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F67FF3D5-9E3D-4039-B5A9-02F075210B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E9406B1-5B9F-4F3B-96C5-F52DA6C8D4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{86AB5B4C-17E6-4005-836C-E492991BD9FD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF0B6334-FAC8-4D4A-BF9A-9C8169B7D6B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-DTCP v2.0" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="259">
   <si>
     <t>Comment</t>
   </si>
@@ -386,7 +386,7 @@
     <t>L4</t>
   </si>
   <si>
-    <t>MLZ2012M1R0HTD25</t>
+    <t>DNF</t>
   </si>
   <si>
     <t>Shielded Multilayer Inductor 1uH ±20% 800mA 130mΩ AEC-Q200 SMD 0805</t>
@@ -482,7 +482,7 @@
     <t>0Ω ±0 0.1W 0603 Thick Film Chip Resistor AEC-Q200 compliant</t>
   </si>
   <si>
-    <t>R4, R8, R9, R10, R11, R12, R13, R14, R15, R16, R17, R25, R29, R37, R41, R45, R48, R51, R58, R59, R60</t>
+    <t>R4, R8, R9, R10, R13, R14, R15, R16, R17, R25, R29, R37, R41, R45, R48, R51, R58, R59, R60</t>
   </si>
   <si>
     <t>FP-RMCF0603-IPC_B</t>
@@ -536,10 +536,7 @@
     <t>CMP-02407-006337-1</t>
   </si>
   <si>
-    <t>DNF</t>
-  </si>
-  <si>
-    <t>R18, R19, R31, R46, R57</t>
+    <t>R11, R12, R18, R19, R31, R46, R57</t>
   </si>
   <si>
     <t>100K 0.1W 1% 0603 (1608 Metric)  SMD</t>
@@ -1214,7 +1211,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45349813-CF69-4290-B23D-0EB5414CFF9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C4BB30-F5A1-4CB2-9CA4-1B7F7AE0C42E}">
   <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1858,7 +1855,7 @@
         <v>149</v>
       </c>
       <c r="F32" s="1">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1923,13 +1920,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>148</v>
@@ -1938,24 +1935,24 @@
         <v>149</v>
       </c>
       <c r="F36" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="F37" s="1">
         <v>2</v>
@@ -1963,19 +1960,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>175</v>
       </c>
       <c r="F38" s="1">
         <v>2</v>
@@ -1983,19 +1980,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="F39" s="1">
         <v>2</v>
@@ -2003,19 +2000,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="F40" s="1">
         <v>1</v>
@@ -2023,19 +2020,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="F41" s="1">
         <v>1</v>
@@ -2043,19 +2040,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="F42" s="1">
         <v>1</v>
@@ -2063,19 +2060,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="F43" s="1">
         <v>1</v>
@@ -2083,19 +2080,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="F44" s="1">
         <v>1</v>
@@ -2103,19 +2100,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="F45" s="1">
         <v>2</v>
@@ -2123,19 +2120,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="F46" s="1">
         <v>1</v>
@@ -2143,19 +2140,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="F47" s="1">
         <v>1</v>
@@ -2163,19 +2160,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>222</v>
-      </c>
       <c r="E48" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F48" s="1">
         <v>1</v>
@@ -2183,19 +2180,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="D49" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="E49" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="F49" s="1">
         <v>2</v>
@@ -2203,19 +2200,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="F50" s="1">
         <v>2</v>
@@ -2223,19 +2220,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="F51" s="1">
         <v>1</v>
@@ -2243,19 +2240,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="F52" s="1">
         <v>1</v>
@@ -2263,19 +2260,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D53" s="2" t="s">
-        <v>246</v>
-      </c>
       <c r="E53" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F53" s="1">
         <v>1</v>
@@ -2283,19 +2280,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="E54" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F54" s="1">
         <v>1</v>
@@ -2303,19 +2300,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="E55" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F55" s="1">
         <v>1</v>
@@ -2323,19 +2320,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="F56" s="1">
         <v>1</v>

--- a/Altium/DTCP v2.0/Project Outputs for DTCP v2.0/Assembly/BOM/Bill of Materials-DTCP v2.0.xlsx
+++ b/Altium/DTCP v2.0/Project Outputs for DTCP v2.0/Assembly/BOM/Bill of Materials-DTCP v2.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerem\AppData\Local\TempReleases\Snapshot\4\Assembly\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jdado\AppData\Local\TempReleases\Snapshot\1\Assembly\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E9406B1-5B9F-4F3B-96C5-F52DA6C8D4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{003A5BA9-3CA8-4C83-9452-0D8DA7B5C82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FF0B6334-FAC8-4D4A-BF9A-9C8169B7D6B4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7704FAD6-8D38-4754-BA3B-7D9FC260E174}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-DTCP v2.0" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
     <t>0Ω ±0 0.1W 0603 Thick Film Chip Resistor AEC-Q200 compliant</t>
   </si>
   <si>
-    <t>R4, R8, R9, R10, R13, R14, R15, R16, R17, R25, R29, R37, R41, R45, R48, R51, R58, R59, R60</t>
+    <t>R4, R8, R9, R10, R13, R14, R15, R16, R17, R25, R29, R37, R41, R45, R48, R51, R53, R54, R56, R58, R59, R60, R62, R63</t>
   </si>
   <si>
     <t>FP-RMCF0603-IPC_B</t>
@@ -1211,14 +1211,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02C4BB30-F5A1-4CB2-9CA4-1B7F7AE0C42E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1120B5BF-788F-4682-B5DF-84D03430BBE4}">
   <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="19.7109375" customWidth="1"/>
+    <col min="1" max="6" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -1278,7 +1278,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>26</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>44</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>49</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>57</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>62</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>66</v>
       </c>
@@ -1518,7 +1518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>71</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>79</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>84</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>89</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>92</v>
       </c>
@@ -1638,7 +1638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>97</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>102</v>
       </c>
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>107</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>112</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>115</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>120</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>125</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>130</v>
       </c>
@@ -1798,7 +1798,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>135</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>140</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>145</v>
       </c>
@@ -1855,10 +1855,10 @@
         <v>149</v>
       </c>
       <c r="F32" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>150</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>155</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>160</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>115</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>115</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>170</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>175</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>179</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>184</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>189</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>194</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>199</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>204</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>209</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>214</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>218</v>
       </c>
@@ -2178,7 +2178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>222</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>227</v>
       </c>
@@ -2218,7 +2218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>232</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>237</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>242</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>246</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>250</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>254</v>
       </c>
@@ -2340,6 +2340,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>